--- a/DataTables/Datas/battle.enemy_behavior_group.xlsx
+++ b/DataTables/Datas/battle.enemy_behavior_group.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R97cd05aaeb05434e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R9eb856bffae24a75"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -421,6 +421,33 @@
         <x:v>7002,7003</x:v>
       </x:c>
     </x:row>
+    <x:row r="7">
+      <x:c r="A7"/>
+      <x:c r="B7" t="n">
+        <x:v>6101</x:v>
+      </x:c>
+      <x:c r="C7" t="str">
+        <x:v>7101,7102</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8"/>
+      <x:c r="B8" t="n">
+        <x:v>6201</x:v>
+      </x:c>
+      <x:c r="C8" t="str">
+        <x:v>7201</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9"/>
+      <x:c r="B9" t="n">
+        <x:v>6202</x:v>
+      </x:c>
+      <x:c r="C9" t="str">
+        <x:v>7202</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
